--- a/pseudodata/2010.xlsx
+++ b/pseudodata/2010.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,60 +451,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Zmin</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Zmax</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>lum</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>lum</t>
+          <t>value</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>stat_u</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>stat_u</t>
+          <t>sys_u</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>sys_u</t>
+          <t>tar</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>tar</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>norm_c</t>
         </is>
@@ -524,43 +519,40 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>0.0004714549741940817</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000732912172919014</v>
+        <v>0.0002980512623443254</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003751348429213463</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.66456086459507e-05</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
+        <v>2.357274870970409e-05</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -578,43 +570,40 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>0.0003969680730897907</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009028821527122683</v>
+        <v>0.0002938374097033703</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005056752933731842</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.514410763561342e-05</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+        <v>1.984840365448953e-05</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -632,43 +621,40 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>0.0002949008183586743</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008517570351968822</v>
+        <v>0.0003166505566215437</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007128140081212664</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.258785175984411e-05</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+        <v>1.474504091793372e-05</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -686,43 +672,40 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>0.0001603032333018029</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000675204108927668</v>
+        <v>0.0003676868577263243</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001016081322065153</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.37602054463834e-05</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+        <v>8.015161665090144e-06</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -740,43 +723,40 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>50</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>-1.154948830978472e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004236826151968522</v>
+        <v>0.0004532007116764985</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001447415600747256</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.118413075984261e-05</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
+        <v>-5.774744154892359e-07</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -794,43 +774,40 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>50</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>-0.0002178847626637237</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001314971968988704</v>
+        <v>0.000583679362935953</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002007221755128722</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6.574859844943523e-06</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+        <v>-1.089423813318619e-05</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -848,43 +825,40 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>50</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>-0.0004425543179043416</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0001246453898194211</v>
+        <v>0.0007734685709133632</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002646684337854862</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-6.232269490971055e-06</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
+        <v>-2.212771589521708e-05</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -902,43 +876,40 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>5.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>50</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>-0.0006530569786415779</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.000104461378325654</v>
+        <v>0.001040838802091241</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003751348429213463</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-5.223068916282702e-06</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+        <v>-3.26528489320789e-05</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -956,43 +927,40 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>50</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>-0.0008011853829809981</v>
       </c>
       <c r="L10" t="n">
-        <v>6.423878474667353e-05</v>
+        <v>0.001408055604745521</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0005056752933731842</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.211939237333677e-06</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+        <v>-4.005926914904991e-05</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1010,43 +978,40 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>50</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>-0.000829478648522017</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001876325197905747</v>
+        <v>0.001898020577532914</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0007128140081212664</v>
-      </c>
-      <c r="N11" t="n">
-        <v>9.381625989528736e-06</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+        <v>-4.147393242610086e-05</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1064,43 +1029,40 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>-0.0006913192045318723</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000248773330653805</v>
+        <v>0.002521802231307262</v>
       </c>
       <c r="M12" t="n">
-        <v>0.001016081322065153</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.243866653269025e-05</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+        <v>-3.456596022659362e-05</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1118,43 +1080,40 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>7.5</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>50</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>-0.000377152435008628</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000257060359501941</v>
+        <v>0.003261695485023105</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001447415600747256</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.285301797509705e-05</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
+        <v>-1.88576217504314e-05</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1172,43 +1131,40 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>50</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>0.0001041029462160145</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002206183857275422</v>
+        <v>0.004080750232885612</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002007221755128722</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.103091928637711e-05</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
+        <v>5.205147310800726e-06</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1226,43 +1182,40 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>8.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>50</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>0.0007950068913187567</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0001679523754007734</v>
+        <v>0.004978404193177839</v>
       </c>
       <c r="M15" t="n">
-        <v>0.002646684337854862</v>
-      </c>
-      <c r="N15" t="n">
-        <v>8.397618770038669e-06</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
+        <v>3.975034456593784e-05</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1280,43 +1233,40 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>50</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>0.001789046136139245</v>
       </c>
       <c r="L16" t="n">
-        <v>1.236351105245078e-06</v>
+        <v>0.006026855999035834</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0003751348429213463</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6.181755526225391e-08</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
+        <v>8.945230680696227e-05</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1334,43 +1284,40 @@
         <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>9.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>50</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>0.003099395501981328</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.488908685336508e-05</v>
+        <v>0.007316559008659544</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0005056752933731842</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-7.444543426682542e-07</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
+        <v>0.0001549697750990664</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1388,259 +1335,40 @@
         <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>50</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>cos(phi_kp)</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>0.004490033032043886</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.993812320315659e-06</v>
+        <v>0.008837662015829079</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0007128140081212664</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-2.996906160157829e-07</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.303799651020565e-05</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.001016081322065153</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.151899825510283e-06</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.327029464978539e-05</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.001447415600747256</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.163514732489269e-06</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.0001025105002842511</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.002007221755128722</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.125525014212558e-06</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.0001390937322778411</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.002646684337854862</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6.954686613892053e-06</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
+        <v>0.0002245016516021943</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
         <v>1</v>
       </c>
     </row>
